--- a/NCU_Mens_Master_ID_Mapping.xlsx
+++ b/NCU_Mens_Master_ID_Mapping.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,6 +26,11 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -54,9 +59,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -422,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2351"/>
+  <dimension ref="A1:F2352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -434,32 +440,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>NV_Play_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>NV_Play_Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Match_Confidence</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Sport80_ID</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Sport80_Name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Sport80_Club</t>
         </is>
@@ -75662,6 +75668,38 @@
       <c r="F2351" t="inlineStr">
         <is>
           <t>PSNI Cricket Club</t>
+        </is>
+      </c>
+    </row>
+    <row r="2352">
+      <c r="A2352" t="inlineStr">
+        <is>
+          <t>bd8ef97e-9065-4eb4-b906-6833b51dc2f8</t>
+        </is>
+      </c>
+      <c r="B2352" t="inlineStr">
+        <is>
+          <t>Zach Cameron</t>
+        </is>
+      </c>
+      <c r="C2352" t="inlineStr">
+        <is>
+          <t>Manual Match</t>
+        </is>
+      </c>
+      <c r="D2352" t="inlineStr">
+        <is>
+          <t>3000001188</t>
+        </is>
+      </c>
+      <c r="E2352" t="inlineStr">
+        <is>
+          <t>Zachary Cameron</t>
+        </is>
+      </c>
+      <c r="F2352" t="inlineStr">
+        <is>
+          <t>CI Cricket Club</t>
         </is>
       </c>
     </row>

--- a/NCU_Mens_Master_ID_Mapping.xlsx
+++ b/NCU_Mens_Master_ID_Mapping.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2352"/>
+  <dimension ref="A1:F2358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -75703,6 +75703,198 @@
         </is>
       </c>
     </row>
+    <row r="2353">
+      <c r="A2353" t="inlineStr">
+        <is>
+          <t>07d5001d-7255-4884-814f-1c0e66167e79</t>
+        </is>
+      </c>
+      <c r="B2353" t="inlineStr">
+        <is>
+          <t>Cameron Kane</t>
+        </is>
+      </c>
+      <c r="C2353" t="inlineStr">
+        <is>
+          <t>Exact Match</t>
+        </is>
+      </c>
+      <c r="D2353" t="inlineStr">
+        <is>
+          <t>2021120676</t>
+        </is>
+      </c>
+      <c r="E2353" t="inlineStr">
+        <is>
+          <t>Cameron Kane</t>
+        </is>
+      </c>
+      <c r="F2353" t="inlineStr">
+        <is>
+          <t>Carrickfergus Cricket Club</t>
+        </is>
+      </c>
+    </row>
+    <row r="2354">
+      <c r="A2354" t="inlineStr">
+        <is>
+          <t>3c1ff6bd-c9d5-479f-b4d5-b6232d98cb05</t>
+        </is>
+      </c>
+      <c r="B2354" t="inlineStr">
+        <is>
+          <t>Prasanth Kumar</t>
+        </is>
+      </c>
+      <c r="C2354" t="inlineStr">
+        <is>
+          <t>Exact Match</t>
+        </is>
+      </c>
+      <c r="D2354" t="inlineStr">
+        <is>
+          <t>3000003403</t>
+        </is>
+      </c>
+      <c r="E2354" t="inlineStr">
+        <is>
+          <t>Prasanth Kumar</t>
+        </is>
+      </c>
+      <c r="F2354" t="inlineStr">
+        <is>
+          <t>Belfast Superkings Cricket Club</t>
+        </is>
+      </c>
+    </row>
+    <row r="2355">
+      <c r="A2355" t="inlineStr">
+        <is>
+          <t>af75d961-76e9-45cd-9ab9-1d5645f4e64a</t>
+        </is>
+      </c>
+      <c r="B2355" t="inlineStr">
+        <is>
+          <t>Joby Kochuvarkey</t>
+        </is>
+      </c>
+      <c r="C2355" t="inlineStr">
+        <is>
+          <t>Exact Match</t>
+        </is>
+      </c>
+      <c r="D2355" t="inlineStr">
+        <is>
+          <t>2021122796</t>
+        </is>
+      </c>
+      <c r="E2355" t="inlineStr">
+        <is>
+          <t>Joby Kochuvarkey</t>
+        </is>
+      </c>
+      <c r="F2355" t="inlineStr">
+        <is>
+          <t>Woodvale Cricket Club</t>
+        </is>
+      </c>
+    </row>
+    <row r="2356">
+      <c r="A2356" t="inlineStr">
+        <is>
+          <t>1c959e44-fe36-4775-a964-aeb63e7985ba</t>
+        </is>
+      </c>
+      <c r="B2356" t="inlineStr">
+        <is>
+          <t>Hridhaan Salian</t>
+        </is>
+      </c>
+      <c r="C2356" t="inlineStr">
+        <is>
+          <t>Exact Match</t>
+        </is>
+      </c>
+      <c r="D2356" t="inlineStr">
+        <is>
+          <t>2021117106</t>
+        </is>
+      </c>
+      <c r="E2356" t="inlineStr">
+        <is>
+          <t>Hridhaan Salian</t>
+        </is>
+      </c>
+      <c r="F2356" t="inlineStr">
+        <is>
+          <t>Instonians Cricket Club</t>
+        </is>
+      </c>
+    </row>
+    <row r="2357">
+      <c r="A2357" t="inlineStr">
+        <is>
+          <t>f22007cd-bec4-469f-a499-d41daab2ef9a</t>
+        </is>
+      </c>
+      <c r="B2357" t="inlineStr">
+        <is>
+          <t>Mark Bell</t>
+        </is>
+      </c>
+      <c r="C2357" t="inlineStr">
+        <is>
+          <t>Exact Match</t>
+        </is>
+      </c>
+      <c r="D2357" t="inlineStr">
+        <is>
+          <t>2021121897</t>
+        </is>
+      </c>
+      <c r="E2357" t="inlineStr">
+        <is>
+          <t>Mark Bell</t>
+        </is>
+      </c>
+      <c r="F2357" t="inlineStr">
+        <is>
+          <t>Carrickfergus Cricket Club</t>
+        </is>
+      </c>
+    </row>
+    <row r="2358">
+      <c r="A2358" t="inlineStr">
+        <is>
+          <t>bb034e5a-6d3a-4860-8088-2fdcdde63c76</t>
+        </is>
+      </c>
+      <c r="B2358" t="inlineStr">
+        <is>
+          <t>Matthew Soeters</t>
+        </is>
+      </c>
+      <c r="C2358" t="inlineStr">
+        <is>
+          <t>Exact Match</t>
+        </is>
+      </c>
+      <c r="D2358" t="inlineStr">
+        <is>
+          <t>3000000554</t>
+        </is>
+      </c>
+      <c r="E2358" t="inlineStr">
+        <is>
+          <t>Matthew Soeters</t>
+        </is>
+      </c>
+      <c r="F2358" t="inlineStr">
+        <is>
+          <t>Carrickfergus Cricket Club</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/NCU_Mens_Master_ID_Mapping.xlsx
+++ b/NCU_Mens_Master_ID_Mapping.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2358"/>
+  <dimension ref="A1:F2359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -440,32 +440,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>NV_Play_ID</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>NV_Play_Name</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Match_Confidence</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Sport80_ID</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Sport80_Name</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Sport80_Club</t>
         </is>
@@ -72691,7 +72691,7 @@
       </c>
       <c r="F2258" t="inlineStr">
         <is>
-          <t>Northern Cricket Union</t>
+          <t>Lisburn Cricket Club</t>
         </is>
       </c>
     </row>
@@ -75076,12 +75076,12 @@
       </c>
       <c r="C2333" t="inlineStr">
         <is>
-          <t>Manual Override (Lapsed)</t>
+          <t>Exact Match</t>
         </is>
       </c>
       <c r="D2333" t="inlineStr">
         <is>
-          <t>2021121374</t>
+          <t>2021113018</t>
         </is>
       </c>
       <c r="E2333" t="inlineStr">
@@ -75620,17 +75620,17 @@
       </c>
       <c r="C2350" t="inlineStr">
         <is>
-          <t>Manual Override (Unregistered)</t>
+          <t>Exact Match</t>
         </is>
       </c>
       <c r="D2350" t="inlineStr">
         <is>
-          <t>Not Registered</t>
+          <t>2021114359</t>
         </is>
       </c>
       <c r="E2350" t="inlineStr">
         <is>
-          <t>Alec Stuart</t>
+          <t>Alex Stuart</t>
         </is>
       </c>
       <c r="F2350" t="inlineStr">
@@ -75892,6 +75892,38 @@
       <c r="F2358" t="inlineStr">
         <is>
           <t>Carrickfergus Cricket Club</t>
+        </is>
+      </c>
+    </row>
+    <row r="2359">
+      <c r="A2359" t="inlineStr">
+        <is>
+          <t>1af71df8-aa95-4dc2-b9c1-beb0a23ffded</t>
+        </is>
+      </c>
+      <c r="B2359" t="inlineStr">
+        <is>
+          <t>Sameer Mohammed</t>
+        </is>
+      </c>
+      <c r="C2359" t="inlineStr">
+        <is>
+          <t>Alias Match</t>
+        </is>
+      </c>
+      <c r="D2359" t="inlineStr">
+        <is>
+          <t>2021113239</t>
+        </is>
+      </c>
+      <c r="E2359" t="inlineStr">
+        <is>
+          <t>Sameer Mohd</t>
+        </is>
+      </c>
+      <c r="F2359" t="inlineStr">
+        <is>
+          <t>Belfast Cricket Club</t>
         </is>
       </c>
     </row>

--- a/NCU_Mens_Master_ID_Mapping.xlsx
+++ b/NCU_Mens_Master_ID_Mapping.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,6 +30,12 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -59,10 +65,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -440,32 +447,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>NV_Play_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>NV_Play_Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Match_Confidence</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Sport80_ID</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Sport80_Name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Sport80_Club</t>
         </is>
@@ -75268,17 +75275,17 @@
       </c>
       <c r="C2339" t="inlineStr">
         <is>
-          <t>Manual Override (Lapsed)</t>
+          <t>Manual Override (Matched)</t>
         </is>
       </c>
       <c r="D2339" t="inlineStr">
         <is>
-          <t>2021121491</t>
+          <t>2021113650</t>
         </is>
       </c>
       <c r="E2339" t="inlineStr">
         <is>
-          <t>Ali Quadri</t>
+          <t>Mubashir Ali</t>
         </is>
       </c>
       <c r="F2339" t="inlineStr">

--- a/NCU_Mens_Master_ID_Mapping.xlsx
+++ b/NCU_Mens_Master_ID_Mapping.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,12 +30,6 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -65,11 +59,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -435,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2359"/>
+  <dimension ref="A1:F2352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -447,32 +440,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>NV_Play_ID</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>NV_Play_Name</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Match_Confidence</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Sport80_ID</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Sport80_Name</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Sport80_Club</t>
         </is>
@@ -72698,7 +72691,7 @@
       </c>
       <c r="F2258" t="inlineStr">
         <is>
-          <t>Lisburn Cricket Club</t>
+          <t>Northern Cricket Union</t>
         </is>
       </c>
     </row>
@@ -75083,12 +75076,12 @@
       </c>
       <c r="C2333" t="inlineStr">
         <is>
-          <t>Exact Match</t>
+          <t>Manual Override (Lapsed)</t>
         </is>
       </c>
       <c r="D2333" t="inlineStr">
         <is>
-          <t>2021113018</t>
+          <t>2021121374</t>
         </is>
       </c>
       <c r="E2333" t="inlineStr">
@@ -75275,17 +75268,17 @@
       </c>
       <c r="C2339" t="inlineStr">
         <is>
-          <t>Manual Override (Matched)</t>
+          <t>Manual Override (Lapsed)</t>
         </is>
       </c>
       <c r="D2339" t="inlineStr">
         <is>
-          <t>2021113650</t>
+          <t>2021121491</t>
         </is>
       </c>
       <c r="E2339" t="inlineStr">
         <is>
-          <t>Mubashir Ali</t>
+          <t>Ali Quadri</t>
         </is>
       </c>
       <c r="F2339" t="inlineStr">
@@ -75627,17 +75620,17 @@
       </c>
       <c r="C2350" t="inlineStr">
         <is>
-          <t>Exact Match</t>
+          <t>Manual Override (Unregistered)</t>
         </is>
       </c>
       <c r="D2350" t="inlineStr">
         <is>
-          <t>2021114359</t>
+          <t>Not Registered</t>
         </is>
       </c>
       <c r="E2350" t="inlineStr">
         <is>
-          <t>Alex Stuart</t>
+          <t>Alec Stuart</t>
         </is>
       </c>
       <c r="F2350" t="inlineStr">
@@ -75707,230 +75700,6 @@
       <c r="F2352" t="inlineStr">
         <is>
           <t>CI Cricket Club</t>
-        </is>
-      </c>
-    </row>
-    <row r="2353">
-      <c r="A2353" t="inlineStr">
-        <is>
-          <t>07d5001d-7255-4884-814f-1c0e66167e79</t>
-        </is>
-      </c>
-      <c r="B2353" t="inlineStr">
-        <is>
-          <t>Cameron Kane</t>
-        </is>
-      </c>
-      <c r="C2353" t="inlineStr">
-        <is>
-          <t>Exact Match</t>
-        </is>
-      </c>
-      <c r="D2353" t="inlineStr">
-        <is>
-          <t>2021120676</t>
-        </is>
-      </c>
-      <c r="E2353" t="inlineStr">
-        <is>
-          <t>Cameron Kane</t>
-        </is>
-      </c>
-      <c r="F2353" t="inlineStr">
-        <is>
-          <t>Carrickfergus Cricket Club</t>
-        </is>
-      </c>
-    </row>
-    <row r="2354">
-      <c r="A2354" t="inlineStr">
-        <is>
-          <t>3c1ff6bd-c9d5-479f-b4d5-b6232d98cb05</t>
-        </is>
-      </c>
-      <c r="B2354" t="inlineStr">
-        <is>
-          <t>Prasanth Kumar</t>
-        </is>
-      </c>
-      <c r="C2354" t="inlineStr">
-        <is>
-          <t>Exact Match</t>
-        </is>
-      </c>
-      <c r="D2354" t="inlineStr">
-        <is>
-          <t>3000003403</t>
-        </is>
-      </c>
-      <c r="E2354" t="inlineStr">
-        <is>
-          <t>Prasanth Kumar</t>
-        </is>
-      </c>
-      <c r="F2354" t="inlineStr">
-        <is>
-          <t>Belfast Superkings Cricket Club</t>
-        </is>
-      </c>
-    </row>
-    <row r="2355">
-      <c r="A2355" t="inlineStr">
-        <is>
-          <t>af75d961-76e9-45cd-9ab9-1d5645f4e64a</t>
-        </is>
-      </c>
-      <c r="B2355" t="inlineStr">
-        <is>
-          <t>Joby Kochuvarkey</t>
-        </is>
-      </c>
-      <c r="C2355" t="inlineStr">
-        <is>
-          <t>Exact Match</t>
-        </is>
-      </c>
-      <c r="D2355" t="inlineStr">
-        <is>
-          <t>2021122796</t>
-        </is>
-      </c>
-      <c r="E2355" t="inlineStr">
-        <is>
-          <t>Joby Kochuvarkey</t>
-        </is>
-      </c>
-      <c r="F2355" t="inlineStr">
-        <is>
-          <t>Woodvale Cricket Club</t>
-        </is>
-      </c>
-    </row>
-    <row r="2356">
-      <c r="A2356" t="inlineStr">
-        <is>
-          <t>1c959e44-fe36-4775-a964-aeb63e7985ba</t>
-        </is>
-      </c>
-      <c r="B2356" t="inlineStr">
-        <is>
-          <t>Hridhaan Salian</t>
-        </is>
-      </c>
-      <c r="C2356" t="inlineStr">
-        <is>
-          <t>Exact Match</t>
-        </is>
-      </c>
-      <c r="D2356" t="inlineStr">
-        <is>
-          <t>2021117106</t>
-        </is>
-      </c>
-      <c r="E2356" t="inlineStr">
-        <is>
-          <t>Hridhaan Salian</t>
-        </is>
-      </c>
-      <c r="F2356" t="inlineStr">
-        <is>
-          <t>Instonians Cricket Club</t>
-        </is>
-      </c>
-    </row>
-    <row r="2357">
-      <c r="A2357" t="inlineStr">
-        <is>
-          <t>f22007cd-bec4-469f-a499-d41daab2ef9a</t>
-        </is>
-      </c>
-      <c r="B2357" t="inlineStr">
-        <is>
-          <t>Mark Bell</t>
-        </is>
-      </c>
-      <c r="C2357" t="inlineStr">
-        <is>
-          <t>Exact Match</t>
-        </is>
-      </c>
-      <c r="D2357" t="inlineStr">
-        <is>
-          <t>2021121897</t>
-        </is>
-      </c>
-      <c r="E2357" t="inlineStr">
-        <is>
-          <t>Mark Bell</t>
-        </is>
-      </c>
-      <c r="F2357" t="inlineStr">
-        <is>
-          <t>Carrickfergus Cricket Club</t>
-        </is>
-      </c>
-    </row>
-    <row r="2358">
-      <c r="A2358" t="inlineStr">
-        <is>
-          <t>bb034e5a-6d3a-4860-8088-2fdcdde63c76</t>
-        </is>
-      </c>
-      <c r="B2358" t="inlineStr">
-        <is>
-          <t>Matthew Soeters</t>
-        </is>
-      </c>
-      <c r="C2358" t="inlineStr">
-        <is>
-          <t>Exact Match</t>
-        </is>
-      </c>
-      <c r="D2358" t="inlineStr">
-        <is>
-          <t>3000000554</t>
-        </is>
-      </c>
-      <c r="E2358" t="inlineStr">
-        <is>
-          <t>Matthew Soeters</t>
-        </is>
-      </c>
-      <c r="F2358" t="inlineStr">
-        <is>
-          <t>Carrickfergus Cricket Club</t>
-        </is>
-      </c>
-    </row>
-    <row r="2359">
-      <c r="A2359" t="inlineStr">
-        <is>
-          <t>1af71df8-aa95-4dc2-b9c1-beb0a23ffded</t>
-        </is>
-      </c>
-      <c r="B2359" t="inlineStr">
-        <is>
-          <t>Sameer Mohammed</t>
-        </is>
-      </c>
-      <c r="C2359" t="inlineStr">
-        <is>
-          <t>Alias Match</t>
-        </is>
-      </c>
-      <c r="D2359" t="inlineStr">
-        <is>
-          <t>2021113239</t>
-        </is>
-      </c>
-      <c r="E2359" t="inlineStr">
-        <is>
-          <t>Sameer Mohd</t>
-        </is>
-      </c>
-      <c r="F2359" t="inlineStr">
-        <is>
-          <t>Belfast Cricket Club</t>
         </is>
       </c>
     </row>
